--- a/data/HS_088/HS_088.xlsx
+++ b/data/HS_088/HS_088.xlsx
@@ -10,8 +10,12 @@
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Catch" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="SPPR" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="PPR" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="NPP" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="sppr_all" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="sppr_inner" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="sppr_PP" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Recycling" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="PPR" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="NPP" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,13 +40,22 @@
       <b val="1"/>
       <sz val="14"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -57,7 +70,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -68,6 +81,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -434,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -512,587 +532,618 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>catch years</t>
+          <t>model workbooks</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1976-2019</t>
+          <t>none yet</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>taxa in catch</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>37</v>
+          <t>catch years</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1976-2019</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>taxa in catch</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>taxa with a trophic level</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B11" t="n">
         <v>32</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>model source context</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>No pilot model selected</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>catch_tonnes</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>ppr_tonnes</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>ppr_over_npp_percent</t>
         </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>1976</v>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="n">
-        <v>17.783</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>1977</v>
-      </c>
-      <c r="B14" t="n">
-        <v>3384</v>
-      </c>
-      <c r="C14" t="n">
-        <v>176101.135</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.0475</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1978</v>
+        <v>1976</v>
       </c>
       <c r="B15" t="n">
-        <v>548</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>19502.849</v>
+        <v>17.783</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0053</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1979</v>
+        <v>1977</v>
       </c>
       <c r="B16" t="n">
-        <v>3589</v>
+        <v>3384</v>
       </c>
       <c r="C16" t="n">
-        <v>175913.221</v>
+        <v>176101.135</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0474</v>
+        <v>0.0053</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1980</v>
+        <v>1978</v>
       </c>
       <c r="B17" t="n">
-        <v>2670</v>
+        <v>548</v>
       </c>
       <c r="C17" t="n">
-        <v>285893.383</v>
+        <v>19502.849</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0771</v>
+        <v>0.0005999999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1981</v>
+        <v>1979</v>
       </c>
       <c r="B18" t="n">
-        <v>6318</v>
+        <v>3589</v>
       </c>
       <c r="C18" t="n">
-        <v>809888.9300000001</v>
+        <v>175913.221</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2183</v>
+        <v>0.0053</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1982</v>
+        <v>1980</v>
       </c>
       <c r="B19" t="n">
-        <v>6742</v>
+        <v>2670</v>
       </c>
       <c r="C19" t="n">
-        <v>277590.808</v>
+        <v>285893.383</v>
       </c>
       <c r="D19" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.0086</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1983</v>
+        <v>1981</v>
       </c>
       <c r="B20" t="n">
-        <v>10678</v>
+        <v>6318</v>
       </c>
       <c r="C20" t="n">
-        <v>401485.138</v>
+        <v>809888.9300000001</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1082</v>
+        <v>0.0243</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1984</v>
+        <v>1982</v>
       </c>
       <c r="B21" t="n">
-        <v>734</v>
+        <v>6742</v>
       </c>
       <c r="C21" t="n">
-        <v>113424.903</v>
+        <v>277590.808</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0306</v>
+        <v>0.0083</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1985</v>
+        <v>1983</v>
       </c>
       <c r="B22" t="n">
-        <v>4814</v>
+        <v>10678</v>
       </c>
       <c r="C22" t="n">
-        <v>120159.026</v>
+        <v>401485.138</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0324</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1986</v>
+        <v>1984</v>
       </c>
       <c r="B23" t="n">
-        <v>3796</v>
+        <v>734</v>
       </c>
       <c r="C23" t="n">
-        <v>132600.689</v>
+        <v>113424.903</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0357</v>
+        <v>0.0034</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1987</v>
+        <v>1985</v>
       </c>
       <c r="B24" t="n">
-        <v>394</v>
+        <v>4814</v>
       </c>
       <c r="C24" t="n">
-        <v>12362.082</v>
+        <v>120159.026</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0033</v>
+        <v>0.0036</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1989</v>
+        <v>1986</v>
       </c>
       <c r="B25" t="n">
-        <v>1110</v>
+        <v>3796</v>
       </c>
       <c r="C25" t="n">
-        <v>211506.14</v>
+        <v>132600.689</v>
       </c>
       <c r="D25" t="n">
-        <v>0.057</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1990</v>
+        <v>1987</v>
       </c>
       <c r="B26" t="n">
-        <v>661</v>
+        <v>394</v>
       </c>
       <c r="C26" t="n">
-        <v>11754.427</v>
+        <v>12362.082</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0032</v>
+        <v>0.0004</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1991</v>
+        <v>1989</v>
       </c>
       <c r="B27" t="n">
-        <v>796</v>
+        <v>1110</v>
       </c>
       <c r="C27" t="n">
-        <v>22793.268</v>
+        <v>211506.14</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0061</v>
+        <v>0.0063</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1997</v>
+        <v>1990</v>
       </c>
       <c r="B28" t="n">
-        <v>0.12</v>
+        <v>661</v>
       </c>
       <c r="C28" t="n">
-        <v>22.866</v>
+        <v>11754.427</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1998</v>
+        <v>1991</v>
       </c>
       <c r="B29" t="n">
-        <v>57.128</v>
+        <v>796</v>
       </c>
       <c r="C29" t="n">
-        <v>72418.75900000001</v>
+        <v>22793.268</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0195</v>
+        <v>0.0007</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1999</v>
+        <v>1997</v>
       </c>
       <c r="B30" t="n">
-        <v>341.89</v>
+        <v>0.12</v>
       </c>
       <c r="C30" t="n">
-        <v>489650.9</v>
+        <v>22.866</v>
       </c>
       <c r="D30" t="n">
-        <v>0.132</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2000</v>
+        <v>1998</v>
       </c>
       <c r="B31" t="n">
-        <v>868.8099999999999</v>
+        <v>57.128</v>
       </c>
       <c r="C31" t="n">
-        <v>1240720.296</v>
+        <v>72418.75900000001</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3344</v>
+        <v>0.0022</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2001</v>
+        <v>1999</v>
       </c>
       <c r="B32" t="n">
-        <v>734.54</v>
+        <v>341.89</v>
       </c>
       <c r="C32" t="n">
-        <v>1041945.395</v>
+        <v>489650.9</v>
       </c>
       <c r="D32" t="n">
-        <v>0.2808</v>
+        <v>0.0147</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="B33" t="n">
-        <v>1799.695</v>
+        <v>868.8099999999999</v>
       </c>
       <c r="C33" t="n">
-        <v>2637362.304</v>
+        <v>1240720.296</v>
       </c>
       <c r="D33" t="n">
-        <v>0.7109</v>
+        <v>0.0372</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="B34" t="n">
-        <v>2201.859</v>
+        <v>734.54</v>
       </c>
       <c r="C34" t="n">
-        <v>3371540.547</v>
+        <v>1041945.395</v>
       </c>
       <c r="D34" t="n">
-        <v>0.9088000000000001</v>
+        <v>0.0312</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="B35" t="n">
-        <v>3781.685</v>
+        <v>1799.695</v>
       </c>
       <c r="C35" t="n">
-        <v>5484431.472</v>
+        <v>2637362.304</v>
       </c>
       <c r="D35" t="n">
-        <v>1.4783</v>
+        <v>0.079</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="B36" t="n">
-        <v>4080.149</v>
+        <v>2201.859</v>
       </c>
       <c r="C36" t="n">
-        <v>5986022.528</v>
+        <v>3371540.547</v>
       </c>
       <c r="D36" t="n">
-        <v>1.6135</v>
+        <v>0.101</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="B37" t="n">
-        <v>3565.323</v>
+        <v>3781.685</v>
       </c>
       <c r="C37" t="n">
-        <v>5478990.164</v>
+        <v>5484431.472</v>
       </c>
       <c r="D37" t="n">
-        <v>1.4768</v>
+        <v>0.1643</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="B38" t="n">
-        <v>3374.637</v>
+        <v>4080.149</v>
       </c>
       <c r="C38" t="n">
-        <v>5094028.405</v>
+        <v>5986022.528</v>
       </c>
       <c r="D38" t="n">
-        <v>1.373</v>
+        <v>0.1793</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="B39" t="n">
-        <v>3265.624</v>
+        <v>3565.323</v>
       </c>
       <c r="C39" t="n">
-        <v>5053482.841</v>
+        <v>5478990.164</v>
       </c>
       <c r="D39" t="n">
-        <v>1.3621</v>
+        <v>0.1641</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="B40" t="n">
-        <v>3746.566</v>
+        <v>3374.637</v>
       </c>
       <c r="C40" t="n">
-        <v>5700861.19</v>
+        <v>5094028.405</v>
       </c>
       <c r="D40" t="n">
-        <v>1.5366</v>
+        <v>0.1526</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="B41" t="n">
-        <v>3898.345</v>
+        <v>3265.624</v>
       </c>
       <c r="C41" t="n">
-        <v>5991136.337</v>
+        <v>5053482.841</v>
       </c>
       <c r="D41" t="n">
-        <v>1.6148</v>
+        <v>0.1513</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="B42" t="n">
-        <v>3346.424</v>
+        <v>3746.566</v>
       </c>
       <c r="C42" t="n">
-        <v>5146074.065</v>
+        <v>5700861.19</v>
       </c>
       <c r="D42" t="n">
-        <v>1.3871</v>
+        <v>0.1707</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="B43" t="n">
-        <v>3615.354</v>
+        <v>3898.345</v>
       </c>
       <c r="C43" t="n">
-        <v>5563968.769</v>
+        <v>5991136.337</v>
       </c>
       <c r="D43" t="n">
-        <v>1.4997</v>
+        <v>0.1794</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="B44" t="n">
-        <v>4350.064</v>
+        <v>3346.424</v>
       </c>
       <c r="C44" t="n">
-        <v>6822871.293</v>
+        <v>5146074.065</v>
       </c>
       <c r="D44" t="n">
-        <v>1.839</v>
+        <v>0.1541</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="B45" t="n">
-        <v>2536.652</v>
+        <v>3615.354</v>
       </c>
       <c r="C45" t="n">
-        <v>3984118.187</v>
+        <v>5563968.769</v>
       </c>
       <c r="D45" t="n">
-        <v>1.0739</v>
+        <v>0.1666</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="B46" t="n">
-        <v>4677.541</v>
+        <v>4350.064</v>
       </c>
       <c r="C46" t="n">
-        <v>7315457.573</v>
+        <v>6822871.293</v>
       </c>
       <c r="D46" t="n">
-        <v>1.9718</v>
+        <v>0.2043</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="B47" t="n">
-        <v>5205.374</v>
+        <v>2536.652</v>
       </c>
       <c r="C47" t="n">
-        <v>7919946.142</v>
+        <v>3984118.187</v>
       </c>
       <c r="D47" t="n">
-        <v>2.1347</v>
+        <v>0.1193</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="B48" t="n">
-        <v>395.803</v>
+        <v>4677.541</v>
       </c>
       <c r="C48" t="n">
-        <v>416407.646</v>
+        <v>7315457.573</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1122</v>
+        <v>0.2191</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="B49" t="n">
-        <v>4401.721</v>
+        <v>5205.374</v>
       </c>
       <c r="C49" t="n">
-        <v>6783433.925</v>
+        <v>7919946.142</v>
       </c>
       <c r="D49" t="n">
-        <v>1.8284</v>
+        <v>0.2372</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B50" t="n">
+        <v>395.803</v>
+      </c>
+      <c r="C50" t="n">
+        <v>416407.646</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.0125</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B51" t="n">
+        <v>4401.721</v>
+      </c>
+      <c r="C51" t="n">
+        <v>6783433.925</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.2032</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
         <v>2019</v>
       </c>
-      <c r="B50" t="n">
+      <c r="B52" t="n">
         <v>3559.328</v>
       </c>
-      <c r="C50" t="n">
+      <c r="C52" t="n">
         <v>5471586.547</v>
       </c>
-      <c r="D50" t="n">
-        <v>1.4748</v>
+      <c r="D52" t="n">
+        <v>0.1639</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>PPR/NPP converts wet-weight PP to carbon at 9:1; NPP is the fixed 2019 ensemble median.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1174,195 +1225,119 @@
           <t>commercial_group</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>1976</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>1977</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>1978</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>1979</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>1980</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>1981</t>
-        </is>
-      </c>
-      <c r="K1" s="2" t="inlineStr">
-        <is>
-          <t>1982</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>1983</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
-          <t>1984</t>
-        </is>
-      </c>
-      <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>1985</t>
-        </is>
-      </c>
-      <c r="O1" s="2" t="inlineStr">
-        <is>
-          <t>1986</t>
-        </is>
-      </c>
-      <c r="P1" s="2" t="inlineStr">
-        <is>
-          <t>1987</t>
-        </is>
-      </c>
-      <c r="Q1" s="2" t="inlineStr">
-        <is>
-          <t>1989</t>
-        </is>
-      </c>
-      <c r="R1" s="2" t="inlineStr">
-        <is>
-          <t>1990</t>
-        </is>
-      </c>
-      <c r="S1" s="2" t="inlineStr">
-        <is>
-          <t>1991</t>
-        </is>
-      </c>
-      <c r="T1" s="2" t="inlineStr">
-        <is>
-          <t>1997</t>
-        </is>
-      </c>
-      <c r="U1" s="2" t="inlineStr">
-        <is>
-          <t>1998</t>
-        </is>
-      </c>
-      <c r="V1" s="2" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="W1" s="2" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="X1" s="2" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="Y1" s="2" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="Z1" s="2" t="inlineStr">
-        <is>
-          <t>2003</t>
-        </is>
-      </c>
-      <c r="AA1" s="2" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
-      </c>
-      <c r="AB1" s="2" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="AC1" s="2" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="AD1" s="2" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="AE1" s="2" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="AF1" s="2" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="AG1" s="2" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="AH1" s="2" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="AI1" s="2" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="AJ1" s="2" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="AK1" s="2" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="AL1" s="2" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="AM1" s="2" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="AN1" s="2" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="AO1" s="2" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="AP1" s="2" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="E1" s="2" t="n">
+        <v>1976</v>
+      </c>
+      <c r="F1" s="2" t="n">
+        <v>1977</v>
+      </c>
+      <c r="G1" s="2" t="n">
+        <v>1978</v>
+      </c>
+      <c r="H1" s="2" t="n">
+        <v>1979</v>
+      </c>
+      <c r="I1" s="2" t="n">
+        <v>1980</v>
+      </c>
+      <c r="J1" s="2" t="n">
+        <v>1981</v>
+      </c>
+      <c r="K1" s="2" t="n">
+        <v>1982</v>
+      </c>
+      <c r="L1" s="2" t="n">
+        <v>1983</v>
+      </c>
+      <c r="M1" s="2" t="n">
+        <v>1984</v>
+      </c>
+      <c r="N1" s="2" t="n">
+        <v>1985</v>
+      </c>
+      <c r="O1" s="2" t="n">
+        <v>1986</v>
+      </c>
+      <c r="P1" s="2" t="n">
+        <v>1987</v>
+      </c>
+      <c r="Q1" s="2" t="n">
+        <v>1989</v>
+      </c>
+      <c r="R1" s="2" t="n">
+        <v>1990</v>
+      </c>
+      <c r="S1" s="2" t="n">
+        <v>1991</v>
+      </c>
+      <c r="T1" s="2" t="n">
+        <v>1997</v>
+      </c>
+      <c r="U1" s="2" t="n">
+        <v>1998</v>
+      </c>
+      <c r="V1" s="2" t="n">
+        <v>1999</v>
+      </c>
+      <c r="W1" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="X1" s="2" t="n">
+        <v>2001</v>
+      </c>
+      <c r="Y1" s="2" t="n">
+        <v>2002</v>
+      </c>
+      <c r="Z1" s="2" t="n">
+        <v>2003</v>
+      </c>
+      <c r="AA1" s="2" t="n">
+        <v>2004</v>
+      </c>
+      <c r="AB1" s="2" t="n">
+        <v>2005</v>
+      </c>
+      <c r="AC1" s="2" t="n">
+        <v>2006</v>
+      </c>
+      <c r="AD1" s="2" t="n">
+        <v>2007</v>
+      </c>
+      <c r="AE1" s="2" t="n">
+        <v>2008</v>
+      </c>
+      <c r="AF1" s="2" t="n">
+        <v>2009</v>
+      </c>
+      <c r="AG1" s="2" t="n">
+        <v>2010</v>
+      </c>
+      <c r="AH1" s="2" t="n">
+        <v>2011</v>
+      </c>
+      <c r="AI1" s="2" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AJ1" s="2" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AK1" s="2" t="n">
+        <v>2014</v>
+      </c>
+      <c r="AL1" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="AM1" s="2" t="n">
+        <v>2016</v>
+      </c>
+      <c r="AN1" s="2" t="n">
+        <v>2017</v>
+      </c>
+      <c r="AO1" s="2" t="n">
+        <v>2018</v>
+      </c>
+      <c r="AP1" s="2" t="n">
+        <v>2019</v>
       </c>
     </row>
     <row r="2">
@@ -6885,6 +6860,245 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Group SPPR: all</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>All basal sources, including imports. Models are separate. Blank means unavailable, not zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>group_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No extracted model is available for this ecosystem.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Group SPPR: inner</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Internal sources: primary producers and detritus; excludes imports. Models are separate. Blank means unavailable, not zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>group_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No extracted model is available for this ecosystem.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Group SPPR: PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Primary producers only; excludes detritus and imports. Models are separate. Blank means unavailable, not zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>group_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No extracted model is available for this ecosystem.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="90" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Recycling diagnostics from diagnose_sppr()</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>b: detrital recycling; rho living: living food-web cycles. Each must be below 1 for convergence; these are necessary, not sufficient checks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>TE_option</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>rho living</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>diagnostic status</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>b converges</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>living converges</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>input balanced</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>configuration</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6999,195 +7213,119 @@
           <t>trophic_level</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>1976</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>1977</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>1978</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>1979</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>1980</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>1981</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>1982</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>1983</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>1984</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>1985</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>1986</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>1987</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>1989</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t>1990</t>
-        </is>
-      </c>
-      <c r="Q4" s="3" t="inlineStr">
-        <is>
-          <t>1991</t>
-        </is>
-      </c>
-      <c r="R4" s="3" t="inlineStr">
-        <is>
-          <t>1997</t>
-        </is>
-      </c>
-      <c r="S4" s="3" t="inlineStr">
-        <is>
-          <t>1998</t>
-        </is>
-      </c>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="V4" s="3" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="W4" s="3" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t>2003</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="AA4" s="3" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="AB4" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="AC4" s="3" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="AD4" s="3" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="AE4" s="3" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="AF4" s="3" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="AG4" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="AH4" s="3" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="AI4" s="3" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="AJ4" s="3" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="AK4" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="AL4" s="3" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="AM4" s="3" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="C4" s="3" t="n">
+        <v>1976</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>1977</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>1978</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>1979</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>1980</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>1981</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>1982</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>1983</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>1984</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>1985</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>1986</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>1987</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>1989</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>1990</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>1991</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>1997</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>1998</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>1999</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>2001</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>2002</v>
+      </c>
+      <c r="X4" s="3" t="n">
+        <v>2003</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>2004</v>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>2005</v>
+      </c>
+      <c r="AA4" s="3" t="n">
+        <v>2006</v>
+      </c>
+      <c r="AB4" s="3" t="n">
+        <v>2007</v>
+      </c>
+      <c r="AC4" s="3" t="n">
+        <v>2008</v>
+      </c>
+      <c r="AD4" s="3" t="n">
+        <v>2009</v>
+      </c>
+      <c r="AE4" s="3" t="n">
+        <v>2010</v>
+      </c>
+      <c r="AF4" s="3" t="n">
+        <v>2011</v>
+      </c>
+      <c r="AG4" s="3" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AH4" s="3" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AI4" s="3" t="n">
+        <v>2014</v>
+      </c>
+      <c r="AJ4" s="3" t="n">
+        <v>2015</v>
+      </c>
+      <c r="AK4" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="AL4" s="3" t="n">
+        <v>2017</v>
+      </c>
+      <c r="AM4" s="3" t="n">
+        <v>2018</v>
+      </c>
+      <c r="AN4" s="3" t="n">
+        <v>2019</v>
       </c>
     </row>
     <row r="5">
@@ -11163,7 +11301,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/data/HS_088/HS_088.xlsx
+++ b/data/HS_088/HS_088.xlsx
@@ -9,15 +9,18 @@
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Catch" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="SPPR" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="sppr_all" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="sppr_inner" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="sppr_PP" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Recycling" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="PPR" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="NPP" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Final mappings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="SPPR" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="sppr_all" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="sppr_inner" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="sppr_PP" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Recycling" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="PPR" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="NPP" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'NPP'!$A$3:$O$41</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -454,13 +457,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -617,9 +620,6 @@
       <c r="C15" t="n">
         <v>17.783</v>
       </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -631,9 +631,6 @@
       <c r="C16" t="n">
         <v>176101.135</v>
       </c>
-      <c r="D16" t="n">
-        <v>0.0053</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -645,9 +642,6 @@
       <c r="C17" t="n">
         <v>19502.849</v>
       </c>
-      <c r="D17" t="n">
-        <v>0.0005999999999999999</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -659,9 +653,6 @@
       <c r="C18" t="n">
         <v>175913.221</v>
       </c>
-      <c r="D18" t="n">
-        <v>0.0053</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -673,9 +664,6 @@
       <c r="C19" t="n">
         <v>285893.383</v>
       </c>
-      <c r="D19" t="n">
-        <v>0.0086</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -687,9 +675,6 @@
       <c r="C20" t="n">
         <v>809888.9300000001</v>
       </c>
-      <c r="D20" t="n">
-        <v>0.0243</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -701,9 +686,6 @@
       <c r="C21" t="n">
         <v>277590.808</v>
       </c>
-      <c r="D21" t="n">
-        <v>0.0083</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -715,9 +697,6 @@
       <c r="C22" t="n">
         <v>401485.138</v>
       </c>
-      <c r="D22" t="n">
-        <v>0.012</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -729,9 +708,6 @@
       <c r="C23" t="n">
         <v>113424.903</v>
       </c>
-      <c r="D23" t="n">
-        <v>0.0034</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -743,9 +719,6 @@
       <c r="C24" t="n">
         <v>120159.026</v>
       </c>
-      <c r="D24" t="n">
-        <v>0.0036</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -757,9 +730,6 @@
       <c r="C25" t="n">
         <v>132600.689</v>
       </c>
-      <c r="D25" t="n">
-        <v>0.004</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -771,9 +741,6 @@
       <c r="C26" t="n">
         <v>12362.082</v>
       </c>
-      <c r="D26" t="n">
-        <v>0.0004</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -785,9 +752,6 @@
       <c r="C27" t="n">
         <v>211506.14</v>
       </c>
-      <c r="D27" t="n">
-        <v>0.0063</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -799,9 +763,6 @@
       <c r="C28" t="n">
         <v>11754.427</v>
       </c>
-      <c r="D28" t="n">
-        <v>0.0004</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -813,9 +774,6 @@
       <c r="C29" t="n">
         <v>22793.268</v>
       </c>
-      <c r="D29" t="n">
-        <v>0.0007</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -827,9 +785,6 @@
       <c r="C30" t="n">
         <v>22.866</v>
       </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -842,7 +797,7 @@
         <v>72418.75900000001</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0022</v>
+        <v>0.0017</v>
       </c>
     </row>
     <row r="32">
@@ -856,7 +811,7 @@
         <v>489650.9</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0147</v>
+        <v>0.0112</v>
       </c>
     </row>
     <row r="33">
@@ -870,7 +825,7 @@
         <v>1240720.296</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0372</v>
+        <v>0.0265</v>
       </c>
     </row>
     <row r="34">
@@ -884,7 +839,7 @@
         <v>1041945.395</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0312</v>
+        <v>0.0225</v>
       </c>
     </row>
     <row r="35">
@@ -898,7 +853,7 @@
         <v>2637362.304</v>
       </c>
       <c r="D35" t="n">
-        <v>0.079</v>
+        <v>0.0575</v>
       </c>
     </row>
     <row r="36">
@@ -912,7 +867,7 @@
         <v>3371540.547</v>
       </c>
       <c r="D36" t="n">
-        <v>0.101</v>
+        <v>0.0752</v>
       </c>
     </row>
     <row r="37">
@@ -926,7 +881,7 @@
         <v>5484431.472</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1643</v>
+        <v>0.1135</v>
       </c>
     </row>
     <row r="38">
@@ -940,7 +895,7 @@
         <v>5986022.528</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1793</v>
+        <v>0.1318</v>
       </c>
     </row>
     <row r="39">
@@ -954,7 +909,7 @@
         <v>5478990.164</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1641</v>
+        <v>0.126</v>
       </c>
     </row>
     <row r="40">
@@ -968,7 +923,7 @@
         <v>5094028.405</v>
       </c>
       <c r="D40" t="n">
-        <v>0.1526</v>
+        <v>0.1299</v>
       </c>
     </row>
     <row r="41">
@@ -982,7 +937,7 @@
         <v>5053482.841</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1513</v>
+        <v>0.1349</v>
       </c>
     </row>
     <row r="42">
@@ -996,7 +951,7 @@
         <v>5700861.19</v>
       </c>
       <c r="D42" t="n">
-        <v>0.1707</v>
+        <v>0.1405</v>
       </c>
     </row>
     <row r="43">
@@ -1010,7 +965,7 @@
         <v>5991136.337</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1794</v>
+        <v>0.1434</v>
       </c>
     </row>
     <row r="44">
@@ -1024,7 +979,7 @@
         <v>5146074.065</v>
       </c>
       <c r="D44" t="n">
-        <v>0.1541</v>
+        <v>0.1195</v>
       </c>
     </row>
     <row r="45">
@@ -1038,7 +993,7 @@
         <v>5563968.769</v>
       </c>
       <c r="D45" t="n">
-        <v>0.1666</v>
+        <v>0.1439</v>
       </c>
     </row>
     <row r="46">
@@ -1052,7 +1007,7 @@
         <v>6822871.293</v>
       </c>
       <c r="D46" t="n">
-        <v>0.2043</v>
+        <v>0.1674</v>
       </c>
     </row>
     <row r="47">
@@ -1066,7 +1021,7 @@
         <v>3984118.187</v>
       </c>
       <c r="D47" t="n">
-        <v>0.1193</v>
+        <v>0.1054</v>
       </c>
     </row>
     <row r="48">
@@ -1080,7 +1035,7 @@
         <v>7315457.573</v>
       </c>
       <c r="D48" t="n">
-        <v>0.2191</v>
+        <v>0.2056</v>
       </c>
     </row>
     <row r="49">
@@ -1094,7 +1049,7 @@
         <v>7919946.142</v>
       </c>
       <c r="D49" t="n">
-        <v>0.2372</v>
+        <v>0.2142</v>
       </c>
     </row>
     <row r="50">
@@ -1108,7 +1063,7 @@
         <v>416407.646</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0125</v>
+        <v>0.0111</v>
       </c>
     </row>
     <row r="51">
@@ -1122,7 +1077,7 @@
         <v>6783433.925</v>
       </c>
       <c r="D51" t="n">
-        <v>0.2032</v>
+        <v>0.1733</v>
       </c>
     </row>
     <row r="52">
@@ -1136,17 +1091,1609 @@
         <v>5471586.547</v>
       </c>
       <c r="D52" t="n">
-        <v>0.1639</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PPR/NPP converts wet-weight PP to carbon at 9:1; NPP is the fixed 2019 ensemble median.</t>
+          <t>PPR/NPP converts wet-weight PP to carbon at 9:1 and uses the matching year's NPP ensemble median.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>PPR/NPP is blank for years without NPP; see NPP for availability and provenance.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="75" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="36" customWidth="1" min="14" max="14"/>
+    <col width="65" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Annual net primary production, tonnes carbon per year</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PPR/NPP uses the ensemble median for the matching catch year. Blank values are unavailable; no year is substituted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>npp_antoinemorel_tC_yr</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>npp_vgpm_tC_yr</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>npp_eppley_tC_yr</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>npp_cbpm_tC_yr</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>npp_cafe_tC_yr</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>ens_median_tC_yr</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>ens_min_tC_yr</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>ens_max_tC_yr</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>n_models</t>
+        </is>
+      </c>
+      <c r="N3" s="7" t="inlineStr">
+        <is>
+          <t>available_models</t>
+        </is>
+      </c>
+      <c r="O3" s="7" t="inlineStr">
+        <is>
+          <t>ensemble_basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1976</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1977</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1978</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1979</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1980</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1981</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1982</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1983</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1984</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1985</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1986</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1987</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1990</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1991</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1997</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B20" t="n">
+        <v>462733941.0760929</v>
+      </c>
+      <c r="G20" t="n">
+        <v>462733941.0760929</v>
+      </c>
+      <c r="H20" t="n">
+        <v>462733941.0760929</v>
+      </c>
+      <c r="I20" t="n">
+        <v>462733941.0760929</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>vgpm: unsupported_year; eppley: unsupported_year; cbpm: unsupported_year; cafe: unsupported_year</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/1998/65dfd93f461846d2/provenance.json</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>antoinemorel</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B21" t="n">
+        <v>485327799.7152657</v>
+      </c>
+      <c r="G21" t="n">
+        <v>485327799.7152657</v>
+      </c>
+      <c r="H21" t="n">
+        <v>485327799.7152657</v>
+      </c>
+      <c r="I21" t="n">
+        <v>485327799.7152657</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>vgpm: unsupported_year; eppley: unsupported_year; cbpm: unsupported_year; cafe: unsupported_year</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/1999/4b1cb2d6cba203fb/provenance.json</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>antoinemorel</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B22" t="n">
+        <v>520027994.5697545</v>
+      </c>
+      <c r="G22" t="n">
+        <v>520027994.5697545</v>
+      </c>
+      <c r="H22" t="n">
+        <v>520027994.5697545</v>
+      </c>
+      <c r="I22" t="n">
+        <v>520027994.5697545</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>vgpm: unsupported_year; eppley: unsupported_year; cbpm: unsupported_year; cafe: unsupported_year</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2000/4bea86f4cd09bd55/provenance.json</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>antoinemorel</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B23" t="n">
+        <v>514032637.8696366</v>
+      </c>
+      <c r="G23" t="n">
+        <v>514032637.8696366</v>
+      </c>
+      <c r="H23" t="n">
+        <v>514032637.8696366</v>
+      </c>
+      <c r="I23" t="n">
+        <v>514032637.8696366</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>vgpm: unsupported_year; eppley: unsupported_year; cbpm: unsupported_year; cafe: unsupported_year</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2001/0ec8617947fb90b9/provenance.json</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>antoinemorel</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B24" t="n">
+        <v>509202042.4783663</v>
+      </c>
+      <c r="G24" t="n">
+        <v>509202042.4783663</v>
+      </c>
+      <c r="H24" t="n">
+        <v>509202042.4783663</v>
+      </c>
+      <c r="I24" t="n">
+        <v>509202042.4783663</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>vgpm: unsupported_year; eppley: unsupported_year; cbpm: unsupported_year; cafe: unsupported_year</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2002/3789d747c9365882/provenance.json</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>antoinemorel</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B25" t="n">
+        <v>517874071.1838095</v>
+      </c>
+      <c r="C25" t="n">
+        <v>345593756.054141</v>
+      </c>
+      <c r="D25" t="n">
+        <v>304305513.210279</v>
+      </c>
+      <c r="E25" t="n">
+        <v>498162948.9167936</v>
+      </c>
+      <c r="F25" t="n">
+        <v>749293834.9077064</v>
+      </c>
+      <c r="G25" t="n">
+        <v>498162948.9167936</v>
+      </c>
+      <c r="H25" t="n">
+        <v>304305513.210279</v>
+      </c>
+      <c r="I25" t="n">
+        <v>749293834.9077064</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2003/c3a820791e3378ef/provenance.json</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>5</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B26" t="n">
+        <v>543903681.1563793</v>
+      </c>
+      <c r="C26" t="n">
+        <v>369524329.2258155</v>
+      </c>
+      <c r="D26" t="n">
+        <v>333595403.3274314</v>
+      </c>
+      <c r="E26" t="n">
+        <v>537135315.8063751</v>
+      </c>
+      <c r="F26" t="n">
+        <v>752283320.2506784</v>
+      </c>
+      <c r="G26" t="n">
+        <v>537135315.8063751</v>
+      </c>
+      <c r="H26" t="n">
+        <v>333595403.3274314</v>
+      </c>
+      <c r="I26" t="n">
+        <v>752283320.2506784</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2004/f4cd3b4c7fc3dd8b/provenance.json</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>5</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B27" t="n">
+        <v>523790581.6804917</v>
+      </c>
+      <c r="C27" t="n">
+        <v>351732761.5274764</v>
+      </c>
+      <c r="D27" t="n">
+        <v>321745242.9521245</v>
+      </c>
+      <c r="E27" t="n">
+        <v>504824864.6464109</v>
+      </c>
+      <c r="F27" t="n">
+        <v>715172028.9806052</v>
+      </c>
+      <c r="G27" t="n">
+        <v>504824864.6464109</v>
+      </c>
+      <c r="H27" t="n">
+        <v>321745242.9521245</v>
+      </c>
+      <c r="I27" t="n">
+        <v>715172028.9806052</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2005/4bdcca026379c2bd/provenance.json</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>5</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B28" t="n">
+        <v>505880407.5857398</v>
+      </c>
+      <c r="C28" t="n">
+        <v>345986070.7152455</v>
+      </c>
+      <c r="D28" t="n">
+        <v>311160159.1325068</v>
+      </c>
+      <c r="E28" t="n">
+        <v>483327999.3755825</v>
+      </c>
+      <c r="F28" t="n">
+        <v>678766713.0025778</v>
+      </c>
+      <c r="G28" t="n">
+        <v>483327999.3755825</v>
+      </c>
+      <c r="H28" t="n">
+        <v>311160159.1325068</v>
+      </c>
+      <c r="I28" t="n">
+        <v>678766713.0025778</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2006/3ea13e28f3d7c994/provenance.json</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>5</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B29" t="n">
+        <v>483271355.5498089</v>
+      </c>
+      <c r="C29" t="n">
+        <v>314801111.5238254</v>
+      </c>
+      <c r="D29" t="n">
+        <v>284967901.9821638</v>
+      </c>
+      <c r="E29" t="n">
+        <v>435595877.9966823</v>
+      </c>
+      <c r="F29" t="n">
+        <v>658937838.2209455</v>
+      </c>
+      <c r="G29" t="n">
+        <v>435595877.9966823</v>
+      </c>
+      <c r="H29" t="n">
+        <v>284967901.9821638</v>
+      </c>
+      <c r="I29" t="n">
+        <v>658937838.2209455</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2007/af2057f32254ca19/provenance.json</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>5</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B30" t="n">
+        <v>490469422.9495296</v>
+      </c>
+      <c r="C30" t="n">
+        <v>323163142.7316129</v>
+      </c>
+      <c r="D30" t="n">
+        <v>298985874.414574</v>
+      </c>
+      <c r="E30" t="n">
+        <v>416254991.1924747</v>
+      </c>
+      <c r="F30" t="n">
+        <v>696948631.3403504</v>
+      </c>
+      <c r="G30" t="n">
+        <v>416254991.1924747</v>
+      </c>
+      <c r="H30" t="n">
+        <v>298985874.414574</v>
+      </c>
+      <c r="I30" t="n">
+        <v>696948631.3403504</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2008/51e4a448b1f4148f/provenance.json</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>5</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B31" t="n">
+        <v>505597999.8001608</v>
+      </c>
+      <c r="C31" t="n">
+        <v>336174613.4375359</v>
+      </c>
+      <c r="D31" t="n">
+        <v>314515204.5864962</v>
+      </c>
+      <c r="E31" t="n">
+        <v>450933543.3123726</v>
+      </c>
+      <c r="F31" t="n">
+        <v>715302566.205736</v>
+      </c>
+      <c r="G31" t="n">
+        <v>450933543.3123726</v>
+      </c>
+      <c r="H31" t="n">
+        <v>314515204.5864962</v>
+      </c>
+      <c r="I31" t="n">
+        <v>715302566.205736</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2009/d16425bc4ac9cb7d/provenance.json</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
+        <v>5</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B32" t="n">
+        <v>535429816.9948266</v>
+      </c>
+      <c r="C32" t="n">
+        <v>373408006.1958813</v>
+      </c>
+      <c r="D32" t="n">
+        <v>346755340.4711953</v>
+      </c>
+      <c r="E32" t="n">
+        <v>464174750.0568796</v>
+      </c>
+      <c r="F32" t="n">
+        <v>753824806.0492629</v>
+      </c>
+      <c r="G32" t="n">
+        <v>464174750.0568796</v>
+      </c>
+      <c r="H32" t="n">
+        <v>346755340.4711953</v>
+      </c>
+      <c r="I32" t="n">
+        <v>753824806.0492629</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2010/5d2cc2c9685a81c9/provenance.json</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>5</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B33" t="n">
+        <v>506414865.5266702</v>
+      </c>
+      <c r="C33" t="n">
+        <v>338168917.5421147</v>
+      </c>
+      <c r="D33" t="n">
+        <v>319754169.5294804</v>
+      </c>
+      <c r="E33" t="n">
+        <v>478519207.7265033</v>
+      </c>
+      <c r="F33" t="n">
+        <v>751807752.9541627</v>
+      </c>
+      <c r="G33" t="n">
+        <v>478519207.7265033</v>
+      </c>
+      <c r="H33" t="n">
+        <v>319754169.5294804</v>
+      </c>
+      <c r="I33" t="n">
+        <v>751807752.9541627</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2011/a6c24b780ceeb354/provenance.json</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>5</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B34" t="n">
+        <v>451897793.989877</v>
+      </c>
+      <c r="C34" t="n">
+        <v>313725799.7924323</v>
+      </c>
+      <c r="D34" t="n">
+        <v>284920927.4008589</v>
+      </c>
+      <c r="E34" t="n">
+        <v>429587642.8866799</v>
+      </c>
+      <c r="F34" t="n">
+        <v>696595382.5907224</v>
+      </c>
+      <c r="G34" t="n">
+        <v>429587642.8866799</v>
+      </c>
+      <c r="H34" t="n">
+        <v>284920927.4008589</v>
+      </c>
+      <c r="I34" t="n">
+        <v>696595382.5907224</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2012/2fd3c52e363d2259/provenance.json</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
+        <v>5</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B35" t="n">
+        <v>452824369.1426685</v>
+      </c>
+      <c r="C35" t="n">
+        <v>328419539.8616164</v>
+      </c>
+      <c r="D35" t="n">
+        <v>289434955.9845093</v>
+      </c>
+      <c r="E35" t="n">
+        <v>461945974.1651073</v>
+      </c>
+      <c r="F35" t="n">
+        <v>685196660.7718265</v>
+      </c>
+      <c r="G35" t="n">
+        <v>452824369.1426685</v>
+      </c>
+      <c r="H35" t="n">
+        <v>289434955.9845093</v>
+      </c>
+      <c r="I35" t="n">
+        <v>685196660.7718265</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2013/821becabd572bab5/provenance.json</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>5</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B36" t="n">
+        <v>466895710.3491324</v>
+      </c>
+      <c r="C36" t="n">
+        <v>327232322.773909</v>
+      </c>
+      <c r="D36" t="n">
+        <v>303941616.8025687</v>
+      </c>
+      <c r="E36" t="n">
+        <v>420123126.1415383</v>
+      </c>
+      <c r="F36" t="n">
+        <v>693307550.8623754</v>
+      </c>
+      <c r="G36" t="n">
+        <v>420123126.1415383</v>
+      </c>
+      <c r="H36" t="n">
+        <v>303941616.8025687</v>
+      </c>
+      <c r="I36" t="n">
+        <v>693307550.8623754</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2014/c9d1725dde41256d/provenance.json</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>5</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B37" t="n">
+        <v>464828710.8993816</v>
+      </c>
+      <c r="C37" t="n">
+        <v>313391489.1479753</v>
+      </c>
+      <c r="D37" t="n">
+        <v>290788826.385192</v>
+      </c>
+      <c r="E37" t="n">
+        <v>395421488.4355173</v>
+      </c>
+      <c r="F37" t="n">
+        <v>656170535.0741459</v>
+      </c>
+      <c r="G37" t="n">
+        <v>395421488.4355173</v>
+      </c>
+      <c r="H37" t="n">
+        <v>290788826.385192</v>
+      </c>
+      <c r="I37" t="n">
+        <v>656170535.0741459</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2015/9d39afaaa8b014f8/provenance.json</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
+        <v>5</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B38" t="n">
+        <v>488009689.2950615</v>
+      </c>
+      <c r="C38" t="n">
+        <v>343659536.5173209</v>
+      </c>
+      <c r="D38" t="n">
+        <v>321005353.1775553</v>
+      </c>
+      <c r="E38" t="n">
+        <v>410844439.1469897</v>
+      </c>
+      <c r="F38" t="n">
+        <v>689621394.2420691</v>
+      </c>
+      <c r="G38" t="n">
+        <v>410844439.1469897</v>
+      </c>
+      <c r="H38" t="n">
+        <v>321005353.1775553</v>
+      </c>
+      <c r="I38" t="n">
+        <v>689621394.2420691</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2016/cfbe2d742214e408/provenance.json</t>
+        </is>
+      </c>
+      <c r="M38" t="n">
+        <v>5</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B39" t="n">
+        <v>465568285.2937538</v>
+      </c>
+      <c r="C39" t="n">
+        <v>367544466.5290069</v>
+      </c>
+      <c r="D39" t="n">
+        <v>333552710.7651067</v>
+      </c>
+      <c r="E39" t="n">
+        <v>416504432.5161567</v>
+      </c>
+      <c r="F39" t="n">
+        <v>703129472.7389953</v>
+      </c>
+      <c r="G39" t="n">
+        <v>416504432.5161567</v>
+      </c>
+      <c r="H39" t="n">
+        <v>333552710.7651067</v>
+      </c>
+      <c r="I39" t="n">
+        <v>703129472.7389953</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2017/e85bc3c6652e1ebf/provenance.json</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
+        <v>5</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B40" t="n">
+        <v>434941219.8867756</v>
+      </c>
+      <c r="C40" t="n">
+        <v>319675655.3026491</v>
+      </c>
+      <c r="D40" t="n">
+        <v>295804082.8566078</v>
+      </c>
+      <c r="E40" t="n">
+        <v>453703065.6648957</v>
+      </c>
+      <c r="F40" t="n">
+        <v>684657778.3296918</v>
+      </c>
+      <c r="G40" t="n">
+        <v>434941219.8867756</v>
+      </c>
+      <c r="H40" t="n">
+        <v>295804082.8566078</v>
+      </c>
+      <c r="I40" t="n">
+        <v>684657778.3296918</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2018/786b5184701484b9/provenance.json</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>5</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B41" t="n">
+        <v>467587768.4362069</v>
+      </c>
+      <c r="C41" t="n">
+        <v>364766039.7816842</v>
+      </c>
+      <c r="D41" t="n">
+        <v>324618762.8131763</v>
+      </c>
+      <c r="E41" t="n">
+        <v>525016556.9959909</v>
+      </c>
+      <c r="F41" t="n">
+        <v>759126312.9582683</v>
+      </c>
+      <c r="G41" t="n">
+        <v>467587768.4362069</v>
+      </c>
+      <c r="H41" t="n">
+        <v>324618762.8131763</v>
+      </c>
+      <c r="I41" t="n">
+        <v>759126312.9582683</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2019/e82a6f61f15e47c4/provenance.json</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>5</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:O41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6383,474 +7930,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Specific PPR for HS_088</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Simple method, applied per taxon: SPPR = (1/TE)^(TL-1), TE = 0.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>taxon</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>trophic_level</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>sppr_simple</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Dissostichus mawsoni</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>4.21</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1621.810097</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Macrouridae</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="C6" t="n">
-        <v>758.577575</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Osteichthyes</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="C7" t="n">
-        <v>616.595002</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Bathyraja</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="C8" t="n">
-        <v>436.515832</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Rajiformes</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="C9" t="n">
-        <v>407.380278</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Macrourus</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="C10" t="n">
-        <v>380.189396</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Pagetodes antarcticus</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="C11" t="n">
-        <v>371.535229</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Macrourus whitsoni</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="C12" t="n">
-        <v>295.120923</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Nototheniidae</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="C13" t="n">
-        <v>269.15348</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Neopagetopsis ionah</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="C14" t="n">
-        <v>263.026799</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Muraenolepis</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="C15" t="n">
-        <v>251.188643</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Muraenolepis microps</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="C16" t="n">
-        <v>251.188643</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Gymnoscopelus nicholsi</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="C17" t="n">
-        <v>245.470892</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Trematomus eulepidotus</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="C18" t="n">
-        <v>223.872114</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Channichthyidae</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="C19" t="n">
-        <v>218.776162</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Myctophidae</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="C20" t="n">
-        <v>199.526231</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Trematomus</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="C21" t="n">
-        <v>194.98446</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Pogonophryne permitini</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="C22" t="n">
-        <v>194.98446</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Gymnoscopelus bolini</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="C23" t="n">
-        <v>194.98446</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Marine fishes not identified</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="C24" t="n">
-        <v>190.546072</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Pleuragramma antarcticum</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="C25" t="n">
-        <v>169.824365</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Chaenodraco wilsoni</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="C26" t="n">
-        <v>169.824365</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Gymnoscopelus fraseri</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="C27" t="n">
-        <v>158.489319</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Artedidraconidae</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="C28" t="n">
-        <v>125.892541</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Lepidonotothen squamifrons</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="C29" t="n">
-        <v>123.026877</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Lithodidae</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="C30" t="n">
-        <v>66.069345</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Notothenia coriiceps</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="C31" t="n">
-        <v>56.234133</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Miscellaneous marine crustaceans</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="C32" t="n">
-        <v>50.118723</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Paralomis</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="C33" t="n">
-        <v>19.952623</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Euphausia superba</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="C34" t="n">
-        <v>17.782794</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Euphausia</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="C35" t="n">
-        <v>15.848932</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Mollusca</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="C36" t="n">
-        <v>12.589254</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>No Ecopath model has been extracted for this ecosystem yet,</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>so the network-based SPPR methods are not available here.</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>No final mappings are available for this ecosystem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Models without a recorded mapping are not assigned invented taxon groups or weights.</t>
         </is>
       </c>
     </row>
@@ -6865,43 +7961,474 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Group SPPR: all</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>All basal sources, including imports. Models are separate. Blank means unavailable, not zero.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>group_name</t>
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Specific PPR for HS_088</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Simple method, applied per taxon: SPPR = (1/TE)^(TL-1), TE = 0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>taxon</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>trophic_level</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>sppr_simple</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>No extracted model is available for this ecosystem.</t>
+          <t>Dissostichus mawsoni</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1621.810097</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Macrouridae</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="C6" t="n">
+        <v>758.577575</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Osteichthyes</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="C7" t="n">
+        <v>616.595002</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Bathyraja</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="C8" t="n">
+        <v>436.515832</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Rajiformes</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="C9" t="n">
+        <v>407.380278</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Macrourus</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="C10" t="n">
+        <v>380.189396</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Pagetodes antarcticus</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="C11" t="n">
+        <v>371.535229</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Macrourus whitsoni</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="C12" t="n">
+        <v>295.120923</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Nototheniidae</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="C13" t="n">
+        <v>269.15348</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Neopagetopsis ionah</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="C14" t="n">
+        <v>263.026799</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Muraenolepis</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C15" t="n">
+        <v>251.188643</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Muraenolepis microps</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C16" t="n">
+        <v>251.188643</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Gymnoscopelus nicholsi</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="C17" t="n">
+        <v>245.470892</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Trematomus eulepidotus</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="C18" t="n">
+        <v>223.872114</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Channichthyidae</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="C19" t="n">
+        <v>218.776162</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Myctophidae</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C20" t="n">
+        <v>199.526231</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Trematomus</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="C21" t="n">
+        <v>194.98446</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Pogonophryne permitini</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="C22" t="n">
+        <v>194.98446</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Gymnoscopelus bolini</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="C23" t="n">
+        <v>194.98446</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Marine fishes not identified</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="C24" t="n">
+        <v>190.546072</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Pleuragramma antarcticum</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="C25" t="n">
+        <v>169.824365</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Chaenodraco wilsoni</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="C26" t="n">
+        <v>169.824365</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Gymnoscopelus fraseri</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C27" t="n">
+        <v>158.489319</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Artedidraconidae</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C28" t="n">
+        <v>125.892541</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Lepidonotothen squamifrons</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="C29" t="n">
+        <v>123.026877</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Lithodidae</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="C30" t="n">
+        <v>66.069345</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Notothenia coriiceps</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C31" t="n">
+        <v>56.234133</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Miscellaneous marine crustaceans</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C32" t="n">
+        <v>50.118723</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Paralomis</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C33" t="n">
+        <v>19.952623</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Euphausia superba</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C34" t="n">
+        <v>17.782794</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Euphausia</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C35" t="n">
+        <v>15.848932</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Mollusca</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C36" t="n">
+        <v>12.589254</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>No Ecopath model has been extracted for this ecosystem yet,</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>so the network-based SPPR methods are not available here.</t>
         </is>
       </c>
     </row>
@@ -6926,14 +8453,14 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Group SPPR: inner</t>
+          <t>Group SPPR: all</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Internal sources: primary producers and detritus; excludes imports. Models are separate. Blank means unavailable, not zero.</t>
+          <t>All basal sources, including imports. Models are separate. Blank means unavailable, not zero.</t>
         </is>
       </c>
     </row>
@@ -6977,14 +8504,14 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Group SPPR: PP</t>
+          <t>Group SPPR: inner</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Primary producers only; excludes detritus and imports. Models are separate. Blank means unavailable, not zero.</t>
+          <t>Internal sources: primary producers and detritus; excludes imports. Models are separate. Blank means unavailable, not zero.</t>
         </is>
       </c>
     </row>
@@ -7013,6 +8540,57 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Group SPPR: PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Primary producers only; excludes detritus and imports. Models are separate. Blank means unavailable, not zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>group_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No extracted model is available for this ecosystem.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7098,7 +8676,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11299,132 +12877,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Net primary production, 2019, tonnes carbon per year</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>satellite_model</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>npp_tC_yr</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Antoine-Morel</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>371002744.1019337</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>VGPM</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>289419892.5835737</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Eppley</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>257565445.2926393</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CbPM</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>416569030.4429682</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CAFE</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>602321027.7065336</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>ensemble median</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>371002744.1019337</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>ensemble min</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>257565445.2926393</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>ensemble max</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>602321027.7065336</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>water area (km2)</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>9249487.844864056</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>